--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488101_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488101_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.057399999999999</v>
+        <v>6.7995</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8692</v>
+        <v>4.1167</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1882</v>
+        <v>2.6828</v>
       </c>
       <c r="G2" t="n">
         <v>2.1846</v>
@@ -610,13 +610,13 @@
         <v>1.3876</v>
       </c>
       <c r="S2" t="n">
-        <v>3.0622</v>
+        <v>1.8042</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0302</v>
+        <v>1.2776</v>
       </c>
       <c r="U2" t="n">
-        <v>1.032</v>
+        <v>0.5266</v>
       </c>
       <c r="V2" t="n">
         <v>2.4142</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1598</v>
+        <v>4.9071</v>
       </c>
       <c r="E3" t="n">
         <v>2.6324</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5274</v>
+        <v>2.2747</v>
       </c>
       <c r="G3" t="n">
         <v>1.4377</v>
@@ -688,13 +688,13 @@
         <v>1.5858</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0502</v>
+        <v>0.7975</v>
       </c>
       <c r="T3" t="n">
         <v>0.6095</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4407</v>
+        <v>0.188</v>
       </c>
       <c r="V3" t="n">
         <v>2.0772</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. CERISUELO QUESADA</t>
+          <t>M. GAMEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.0095</v>
+        <v>4.5402</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2206</v>
+        <v>2.5403</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7888</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6982</v>
+        <v>4.186</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5261</v>
+        <v>2.2554</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1721</v>
+        <v>1.9306</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3335</v>
+        <v>3.1422</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1728</v>
+        <v>1.3588</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1607</v>
+        <v>1.7834</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3647</v>
+        <v>1.0438</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3533</v>
+        <v>0.8966</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0114</v>
+        <v>0.1472</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3964</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5947</v>
+        <v>0.7929</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4411</v>
+        <v>0.5524</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6116</v>
+        <v>0.3892</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8294</v>
+        <v>0.1632</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W. EL OTMANI MOHAMED</t>
+          <t>S. CURBELO MENENDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.0911</v>
+        <v>4.4409</v>
       </c>
       <c r="E5" t="n">
-        <v>2.915</v>
+        <v>3.3147</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1762</v>
+        <v>1.1262</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5836</v>
+        <v>2.8468</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4301</v>
+        <v>1.8844</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1535</v>
+        <v>0.9625</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1565</v>
+        <v>2.8971</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4105</v>
+        <v>2.2063</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.254</v>
+        <v>0.6908</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4271</v>
+        <v>-0.0503</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0196</v>
+        <v>-0.3219</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4075</v>
+        <v>0.2717</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3876</v>
+        <v>1.5858</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3876</v>
+        <v>1.5858</v>
       </c>
       <c r="S5" t="n">
-        <v>1.783</v>
+        <v>0.0083</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1549</v>
+        <v>0.4176</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3719</v>
+        <v>-0.4094</v>
       </c>
       <c r="V5" t="n">
-        <v>0.337</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. CHEKRI KOURAYCHE</t>
+          <t>A. MARTIN BONNEMAISON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.0449</v>
+        <v>4.2948</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8633</v>
+        <v>1.9385</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1816</v>
+        <v>2.3563</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7074</v>
+        <v>3.9645</v>
       </c>
       <c r="H6" t="n">
-        <v>1.8844</v>
+        <v>2.5984</v>
       </c>
       <c r="I6" t="n">
-        <v>0.823</v>
+        <v>1.366</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8043</v>
+        <v>2.6643</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8569</v>
+        <v>1.9774</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9474</v>
+        <v>0.6869</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.097</v>
+        <v>1.3002</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0275</v>
+        <v>0.621</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1244</v>
+        <v>0.6791</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1893</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7929</v>
+        <v>0.3964</v>
       </c>
       <c r="S6" t="n">
-        <v>2.7934</v>
+        <v>0.925</v>
       </c>
       <c r="T6" t="n">
-        <v>2.0412</v>
+        <v>0.2653</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7522</v>
+        <v>0.6597</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. MARTIN BONNEMAISON</t>
+          <t>J. CERISUELO QUESADA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.857</v>
+        <v>3.9137</v>
       </c>
       <c r="E7" t="n">
-        <v>1.978</v>
+        <v>2.4057</v>
       </c>
       <c r="F7" t="n">
-        <v>1.879</v>
+        <v>1.508</v>
       </c>
       <c r="G7" t="n">
-        <v>3.9645</v>
+        <v>2.6982</v>
       </c>
       <c r="H7" t="n">
-        <v>2.5984</v>
+        <v>2.5261</v>
       </c>
       <c r="I7" t="n">
-        <v>1.366</v>
+        <v>0.1721</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6643</v>
+        <v>2.3335</v>
       </c>
       <c r="K7" t="n">
-        <v>1.9774</v>
+        <v>2.1728</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6869</v>
+        <v>0.1607</v>
       </c>
       <c r="M7" t="n">
-        <v>1.3002</v>
+        <v>0.3647</v>
       </c>
       <c r="N7" t="n">
-        <v>0.621</v>
+        <v>0.3533</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6791</v>
+        <v>0.0114</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5947</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3964</v>
+        <v>0.5947</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4871</v>
+        <v>1.3453</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3047</v>
+        <v>0.7967</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1824</v>
+        <v>0.5486</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. CURBELO MENENDEZ</t>
+          <t>T. LIBERATORE DARGAM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.4679</v>
+        <v>3.5646</v>
       </c>
       <c r="E8" t="n">
-        <v>2.3979</v>
+        <v>4.1846</v>
       </c>
       <c r="F8" t="n">
-        <v>1.07</v>
+        <v>-0.62</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8468</v>
+        <v>4.3097</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8844</v>
+        <v>1.061</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9625</v>
+        <v>3.2487</v>
       </c>
       <c r="J8" t="n">
-        <v>2.8971</v>
+        <v>4.4805</v>
       </c>
       <c r="K8" t="n">
-        <v>2.2063</v>
+        <v>1.379</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6908</v>
+        <v>3.1015</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0503</v>
+        <v>-0.1708</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3219</v>
+        <v>-0.318</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2717</v>
+        <v>0.1472</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5858</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5858</v>
+        <v>0.7929</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9647</v>
+        <v>0.3937</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4992</v>
+        <v>0.4287</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4655</v>
+        <v>-0.035</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.9405</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. GAMEZ SANCHEZ</t>
+          <t>D. MALAVE FERNANDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>3.1575</v>
+        <v>3.3904</v>
       </c>
       <c r="E9" t="n">
-        <v>1.6629</v>
+        <v>1.6037</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4945</v>
+        <v>1.7867</v>
       </c>
       <c r="G9" t="n">
-        <v>4.186</v>
+        <v>3.2653</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2554</v>
+        <v>0.8297</v>
       </c>
       <c r="I9" t="n">
-        <v>1.9306</v>
+        <v>2.4355</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1422</v>
+        <v>2.5783</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3588</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>1.7834</v>
+        <v>1.8922</v>
       </c>
       <c r="M9" t="n">
-        <v>1.0438</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8966</v>
+        <v>0.1437</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1472</v>
+        <v>0.5433</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1982</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7929</v>
+        <v>0.1982</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8303</v>
+        <v>0.2441</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4881</v>
+        <v>0.0165</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3422</v>
+        <v>0.2275</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.674</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. MALAVE FERNANDEZ</t>
+          <t>W. EL OTMANI MOHAMED</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>2.9496</v>
+        <v>3.3708</v>
       </c>
       <c r="E10" t="n">
-        <v>1.2752</v>
+        <v>1.9981</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6744</v>
+        <v>1.3727</v>
       </c>
       <c r="G10" t="n">
-        <v>3.2653</v>
+        <v>0.5836</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8297</v>
+        <v>0.4301</v>
       </c>
       <c r="I10" t="n">
-        <v>2.4355</v>
+        <v>0.1535</v>
       </c>
       <c r="J10" t="n">
-        <v>2.5783</v>
+        <v>0.1565</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.4105</v>
       </c>
       <c r="L10" t="n">
-        <v>1.8922</v>
+        <v>-0.254</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.4271</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1437</v>
+        <v>0.0196</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5433</v>
+        <v>0.4075</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7929</v>
+        <v>1.3876</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1982</v>
+        <v>1.3876</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1968</v>
+        <v>1.0627</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.312</v>
+        <v>1.2381</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1152</v>
+        <v>-0.1754</v>
       </c>
       <c r="V10" t="n">
-        <v>0.674</v>
+        <v>0.337</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X10" t="n">
-        <v>0.674</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. LIBERATORE DARGAM</t>
+          <t>F. CHEKRI KOURAYCHE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>2.2422</v>
+        <v>2.7078</v>
       </c>
       <c r="E11" t="n">
-        <v>3.143</v>
+        <v>2.275</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9006999999999999</v>
+        <v>0.4328</v>
       </c>
       <c r="G11" t="n">
-        <v>4.3097</v>
+        <v>2.7074</v>
       </c>
       <c r="H11" t="n">
-        <v>1.061</v>
+        <v>1.8844</v>
       </c>
       <c r="I11" t="n">
-        <v>3.2487</v>
+        <v>0.823</v>
       </c>
       <c r="J11" t="n">
-        <v>4.4805</v>
+        <v>2.8043</v>
       </c>
       <c r="K11" t="n">
-        <v>1.379</v>
+        <v>1.8569</v>
       </c>
       <c r="L11" t="n">
-        <v>3.1015</v>
+        <v>0.9474</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1708</v>
+        <v>-0.097</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.318</v>
+        <v>0.0275</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1472</v>
+        <v>-0.1244</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1982</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R11" t="n">
         <v>0.7929</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9287</v>
+        <v>1.4563</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6129</v>
+        <v>1.4529</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3158</v>
+        <v>0.0034</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9405</v>
+        <v>-0.2666</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2071</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.5963</v>
+        <v>1.118</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0015</v>
+        <v>-0.1428</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5978</v>
+        <v>1.2608</v>
       </c>
       <c r="G12" t="n">
         <v>2.1545</v>
@@ -1390,13 +1390,13 @@
         <v>0.7929</v>
       </c>
       <c r="S12" t="n">
-        <v>1.8383</v>
+        <v>1.36</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8701</v>
+        <v>0.7288</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.6312</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2071</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>43.6332</v>
+        <v>43.0478</v>
       </c>
       <c r="E13" t="n">
-        <v>26.956</v>
+        <v>26.8669</v>
       </c>
       <c r="F13" t="n">
-        <v>16.6772</v>
+        <v>16.181</v>
       </c>
       <c r="G13" t="n">
         <v>30.3383</v>
@@ -1450,13 +1450,13 @@
         <v>11.3949</v>
       </c>
       <c r="M13" t="n">
-        <v>5.818000000000001</v>
+        <v>5.818</v>
       </c>
       <c r="N13" t="n">
         <v>2.0938</v>
       </c>
       <c r="O13" t="n">
-        <v>3.724299999999999</v>
+        <v>3.7243</v>
       </c>
       <c r="P13" t="n">
         <v>-0.5945</v>
@@ -1468,13 +1468,13 @@
         <v>10.3077</v>
       </c>
       <c r="S13" t="n">
-        <v>10.5348</v>
+        <v>9.949499999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>7.71</v>
+        <v>7.620900000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>2.8247</v>
+        <v>2.3284</v>
       </c>
       <c r="V13" t="n">
         <v>3.3548</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. TERRON FERNANDEZ</t>
+          <t>R. VIDALES MOLINA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.2418</v>
+        <v>-1.354</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9089</v>
+        <v>1.1522</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.1507</v>
+        <v>-2.5062</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1452</v>
+        <v>-1.6516</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6605</v>
+        <v>1.2049</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.5153</v>
+        <v>-2.8565</v>
       </c>
       <c r="J15" t="n">
-        <v>2.841</v>
+        <v>1.5215</v>
       </c>
       <c r="K15" t="n">
-        <v>3.5927</v>
+        <v>3.4786</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.7517</v>
+        <v>-1.957</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.6958</v>
+        <v>-3.1732</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.9322</v>
+        <v>-2.2737</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7635999999999999</v>
+        <v>-0.8995</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3964</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3876</v>
+        <v>1.1893</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9133</v>
+        <v>-0.6497000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0589</v>
+        <v>-0.1274</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9723000000000001</v>
+        <v>-0.5224</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.8701</v>
+        <v>1.7403</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.7403</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.8701</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. VIDALES MOLINA</t>
+          <t>D. TERRON FERNANDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.8235</v>
+        <v>-1.7721</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8466</v>
+        <v>1.6033</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.6701</v>
+        <v>-3.3753</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.6516</v>
+        <v>0.1452</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2049</v>
+        <v>1.6605</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.8565</v>
+        <v>-1.5153</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5215</v>
+        <v>2.841</v>
       </c>
       <c r="K16" t="n">
-        <v>3.4786</v>
+        <v>3.5927</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.957</v>
+        <v>-0.7517</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.1732</v>
+        <v>-2.6958</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.2737</v>
+        <v>-1.9322</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8995</v>
+        <v>-0.7635999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.7929</v>
+        <v>0.3964</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1893</v>
+        <v>1.3876</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1193</v>
+        <v>-1.4436</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.433</v>
+        <v>-0.2467</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6863</v>
+        <v>-1.1969</v>
       </c>
       <c r="V16" t="n">
-        <v>1.7403</v>
+        <v>-0.8701</v>
       </c>
       <c r="W16" t="n">
-        <v>1.7403</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.0865</v>
+        <v>-3.5057</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4684</v>
+        <v>-0.1429</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.5549</v>
+        <v>-3.3629</v>
       </c>
       <c r="G17" t="n">
         <v>-3.5043</v>
@@ -1780,13 +1780,13 @@
         <v>1.1893</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.168</v>
+        <v>-0.5873</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3085</v>
+        <v>-0.3027</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4766</v>
+        <v>-0.2846</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6036</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.742</v>
+        <v>-4.6192</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.1209</v>
+        <v>-2.2227</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.6211</v>
+        <v>-2.3965</v>
       </c>
       <c r="G18" t="n">
         <v>-0.7252</v>
@@ -1858,13 +1858,13 @@
         <v>0.7929</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.9573</v>
+        <v>-1.8345</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3082</v>
+        <v>-0.4101</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.6491</v>
+        <v>-1.4244</v>
       </c>
       <c r="V18" t="n">
         <v>-0.8701</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-8.400700000000001</v>
+        <v>-7.2429</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.8474</v>
+        <v>-4.1343</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.5533</v>
+        <v>-3.1086</v>
       </c>
       <c r="G19" t="n">
         <v>-5.3323</v>
@@ -1936,13 +1936,13 @@
         <v>1.3876</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.4737</v>
+        <v>-1.3159</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0497</v>
+        <v>-0.3366</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.424</v>
+        <v>-0.9792999999999999</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-8.538500000000001</v>
+        <v>-8.6861</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.5943</v>
+        <v>-5.7981</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.9442</v>
+        <v>-2.8881</v>
       </c>
       <c r="G20" t="n">
         <v>-6.6379</v>
@@ -2014,13 +2014,13 @@
         <v>1.1893</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1078</v>
+        <v>-1.2554</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2972</v>
+        <v>-0.5009</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8106</v>
+        <v>-0.7544999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. WOLKOWYSKI</t>
+          <t>F. MONTIEL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-9.5952</v>
+        <v>-9.783300000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.6583</v>
+        <v>-5.8891</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.9369</v>
+        <v>-3.8942</v>
       </c>
       <c r="G21" t="n">
-        <v>-7.1586</v>
+        <v>-8.2784</v>
       </c>
       <c r="H21" t="n">
-        <v>-4.4262</v>
+        <v>-5.7107</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.7324</v>
+        <v>-2.5677</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.2521</v>
+        <v>-4.1017</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.2922</v>
+        <v>-3.5029</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0402</v>
+        <v>-0.5988</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.9065</v>
+        <v>-4.1767</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.134</v>
+        <v>-2.2078</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.7725</v>
+        <v>-1.969</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1982</v>
+        <v>0.9911</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R21" t="n">
-        <v>1.784</v>
+        <v>1.9822</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9609</v>
+        <v>-1.0223</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2499</v>
+        <v>-0.7963</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.2109</v>
+        <v>-0.226</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2775</v>
+        <v>-1.4737</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.674</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6036</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. MONTIEL RODRIGUEZ</t>
+          <t>T. WOLKOWYSKI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-10.2287</v>
+        <v>-10.0144</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.7041</v>
+        <v>-5.2695</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.5246</v>
+        <v>-4.7449</v>
       </c>
       <c r="G22" t="n">
-        <v>-8.2784</v>
+        <v>-7.1586</v>
       </c>
       <c r="H22" t="n">
-        <v>-5.7107</v>
+        <v>-4.4262</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.5677</v>
+        <v>-2.7324</v>
       </c>
       <c r="J22" t="n">
-        <v>-4.1017</v>
+        <v>-2.2521</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.5029</v>
+        <v>-2.2922</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5988</v>
+        <v>0.0402</v>
       </c>
       <c r="M22" t="n">
-        <v>-4.1767</v>
+        <v>-4.9065</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.2078</v>
+        <v>-2.134</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.969</v>
+        <v>-2.7725</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9911</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9822</v>
+        <v>1.784</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4677</v>
+        <v>-1.3802</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.6113</v>
+        <v>-0.3613</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1436</v>
+        <v>-1.0189</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.4737</v>
+        <v>-1.2775</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.4737</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-47.05160000000001</v>
+        <v>-46.3724</v>
       </c>
       <c r="E23" t="n">
         <v>-20.0958</v>
       </c>
       <c r="F23" t="n">
-        <v>-26.9558</v>
+        <v>-26.27670000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-32.5378</v>
@@ -2227,7 +2227,7 @@
         <v>-2.5831</v>
       </c>
       <c r="L23" t="n">
-        <v>-4.810899999999999</v>
+        <v>-4.810900000000001</v>
       </c>
       <c r="M23" t="n">
         <v>-25.1438</v>
@@ -2239,7 +2239,7 @@
         <v>-11.7966</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9912000000000002</v>
+        <v>-0.9912000000000001</v>
       </c>
       <c r="Q23" t="n">
         <v>-11.8932</v>
@@ -2248,13 +2248,13 @@
         <v>10.9022</v>
       </c>
       <c r="S23" t="n">
-        <v>-10.168</v>
+        <v>-9.488900000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.0821</v>
+        <v>-3.082</v>
       </c>
       <c r="U23" t="n">
-        <v>-7.0862</v>
+        <v>-6.407</v>
       </c>
       <c r="V23" t="n">
         <v>-3.3547</v>
@@ -2263,7 +2263,7 @@
         <v>2.2734</v>
       </c>
       <c r="X23" t="n">
-        <v>-5.628200000000001</v>
+        <v>-5.6282</v>
       </c>
     </row>
   </sheetData>
